--- a/Presupuestos/7.-SDTI 2026 - aprobado.xlsx
+++ b/Presupuestos/7.-SDTI 2026 - aprobado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Presupuestos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\proyecto-ippi\Presupuestos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD26E66-9623-4877-B949-1E01FC6DC3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1400A48F-FE30-43A9-818B-6363C89238C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3B2412E4-D0CB-4FFA-9D79-3FC8DE82B70F}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B2412E4-D0CB-4FFA-9D79-3FC8DE82B70F}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO PRESUPUESTO GRAL" sheetId="1" r:id="rId1"/>
